--- a/Hardware/Design/Issue Log.xlsx
+++ b/Hardware/Design/Issue Log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/69f5ad8fb782b24f/Documents/GitHub/Home-Audio-System/Hardware/Design/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://indesignllc1-my.sharepoint.com/personal/adwolfe_indesign-llc_com/Documents/M_Drive/Github/Home-Audio-System/Hardware/Design/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="11_F25DC773A252ABDACC1048A061DA4FC05ADE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA8884E6-10EE-4623-BAC9-DF64C3FD5A05}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="11_F25DC773A252ABDACC1048A061DA4FC05ADE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E910553C-1F48-4C9C-B5E6-C2722C52DA11}"/>
   <bookViews>
-    <workbookView xWindow="8730" yWindow="2370" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>All input sources cannot be selected</t>
   </si>
@@ -43,6 +43,18 @@
   </si>
   <si>
     <t>change R191 to 51.4k</t>
+  </si>
+  <si>
+    <t>100k pullups are needed on fets that drive 7 segment characters</t>
+  </si>
+  <si>
+    <t>LED driver shift register cannot pull it up</t>
+  </si>
+  <si>
+    <t>op amps that run from FM and BT radios draw very high current</t>
+  </si>
+  <si>
+    <t>Enable 2V5 LDO with micro to sequence supplies to prevent latch up in op amps</t>
   </si>
 </sst>
 </file>
@@ -99,10 +111,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -368,12 +376,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:E5"/>
+  <dimension ref="B3:E7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.42578125" customWidth="1"/>
+    <col min="4" max="4" width="58.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:5" ht="45" x14ac:dyDescent="0.25">
@@ -418,6 +426,34 @@
         <v>4</v>
       </c>
     </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6" s="1">
+        <v>45845</v>
+      </c>
+      <c r="D6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1">
+        <v>45845</v>
+      </c>
+      <c r="D7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Hardware/Design/Issue Log.xlsx
+++ b/Hardware/Design/Issue Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://indesignllc1-my.sharepoint.com/personal/adwolfe_indesign-llc_com/Documents/M_Drive/Github/Home-Audio-System/Hardware/Design/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="11_F25DC773A252ABDACC1048A061DA4FC05ADE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E910553C-1F48-4C9C-B5E6-C2722C52DA11}"/>
+  <xr:revisionPtr revIDLastSave="45" documentId="11_F25DC773A252ABDACC1048A061DA4FC05ADE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3C04EE6-37F3-4380-AE6B-09BBE114F8C8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>All input sources cannot be selected</t>
   </si>
@@ -54,7 +54,13 @@
     <t>op amps that run from FM and BT radios draw very high current</t>
   </si>
   <si>
-    <t>Enable 2V5 LDO with micro to sequence supplies to prevent latch up in op amps</t>
+    <t>Enable 2V5 LDO with pin 35, RF6 on micro to sequence supplies to prevent latch up in op amps</t>
+  </si>
+  <si>
+    <t>rotary encoders do not function right</t>
+  </si>
+  <si>
+    <t>pull up data lines to 3V3 and pull common down to ground</t>
   </si>
 </sst>
 </file>
@@ -376,7 +382,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:E7"/>
+  <dimension ref="B3:E8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -454,6 +460,20 @@
         <v>9</v>
       </c>
     </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8" s="1">
+        <v>45846</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Hardware/Design/Issue Log.xlsx
+++ b/Hardware/Design/Issue Log.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://indesignllc1-my.sharepoint.com/personal/adwolfe_indesign-llc_com/Documents/M_Drive/Github/Home-Audio-System/Hardware/Design/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="45" documentId="11_F25DC773A252ABDACC1048A061DA4FC05ADE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3C04EE6-37F3-4380-AE6B-09BBE114F8C8}"/>
+  <xr:revisionPtr revIDLastSave="50" documentId="11_F25DC773A252ABDACC1048A061DA4FC05ADE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{123B6086-87E4-4414-9D2C-9BAD61E890DC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>All input sources cannot be selected</t>
   </si>
@@ -61,6 +61,9 @@
   </si>
   <si>
     <t>pull up data lines to 3V3 and pull common down to ground</t>
+  </si>
+  <si>
+    <t>IC45 isn't getting 2.5V to pin 3</t>
   </si>
 </sst>
 </file>
@@ -382,7 +385,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:E8"/>
+  <dimension ref="B3:E10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -474,6 +477,17 @@
         <v>11</v>
       </c>
     </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B10">
+        <v>8</v>
+      </c>
+      <c r="C10" s="1">
+        <v>45860</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Hardware/Design/Issue Log.xlsx
+++ b/Hardware/Design/Issue Log.xlsx
@@ -8,24 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://indesignllc1-my.sharepoint.com/personal/adwolfe_indesign-llc_com/Documents/M_Drive/Github/Home-Audio-System/Hardware/Design/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="11_F25DC773A252ABDACC1048A061DA4FC05ADE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{123B6086-87E4-4414-9D2C-9BAD61E890DC}"/>
+  <xr:revisionPtr revIDLastSave="67" documentId="11_F25DC773A252ABDACC1048A061DA4FC05ADE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD3596A1-1818-4921-BAEB-20CB1E264AF2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
   <si>
     <t>All input sources cannot be selected</t>
   </si>
@@ -64,6 +75,21 @@
   </si>
   <si>
     <t>IC45 isn't getting 2.5V to pin 3</t>
+  </si>
+  <si>
+    <t>Transistors thermal pads are shorting together and to the ground of the board</t>
+  </si>
+  <si>
+    <t>buy silicone thermal pads for transistor heat sinks, and trim off heatsink legs</t>
+  </si>
+  <si>
+    <t>not done</t>
+  </si>
+  <si>
+    <t>done</t>
+  </si>
+  <si>
+    <t>white wire to 2V5 net</t>
   </si>
 </sst>
 </file>
@@ -385,15 +411,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:E10"/>
+  <dimension ref="B3:F11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="58.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="71.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="86" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:6" ht="45" x14ac:dyDescent="0.25">
       <c r="B3">
         <v>1</v>
       </c>
@@ -406,8 +432,11 @@
       <c r="E3" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>2</v>
       </c>
@@ -420,8 +449,11 @@
       <c r="E4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>3</v>
       </c>
@@ -434,8 +466,11 @@
       <c r="E5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>4</v>
       </c>
@@ -448,8 +483,11 @@
       <c r="E6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>5</v>
       </c>
@@ -462,8 +500,11 @@
       <c r="E7" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>6</v>
       </c>
@@ -476,8 +517,11 @@
       <c r="E8" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>8</v>
       </c>
@@ -486,6 +530,29 @@
       </c>
       <c r="D10" t="s">
         <v>12</v>
+      </c>
+      <c r="E10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B11">
+        <v>9</v>
+      </c>
+      <c r="C11" s="1">
+        <v>45862</v>
+      </c>
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/Hardware/Design/Issue Log.xlsx
+++ b/Hardware/Design/Issue Log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://indesignllc1-my.sharepoint.com/personal/adwolfe_indesign-llc_com/Documents/M_Drive/Github/Home-Audio-System/Hardware/Design/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="67" documentId="11_F25DC773A252ABDACC1048A061DA4FC05ADE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD3596A1-1818-4921-BAEB-20CB1E264AF2}"/>
+  <xr:revisionPtr revIDLastSave="96" documentId="11_F25DC773A252ABDACC1048A061DA4FC05ADE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68EBBC3B-8D0D-43E5-BF62-F9840F2286C4}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="29">
   <si>
     <t>All input sources cannot be selected</t>
   </si>
@@ -90,6 +90,39 @@
   </si>
   <si>
     <t>white wire to 2V5 net</t>
+  </si>
+  <si>
+    <t>item</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>issue description</t>
+  </si>
+  <si>
+    <t>solution</t>
+  </si>
+  <si>
+    <t>fixed?</t>
+  </si>
+  <si>
+    <t>bandpass filter circuits vary wildly with how much the peak amplitude comes out to be</t>
+  </si>
+  <si>
+    <t>potentially improve in V2 design</t>
+  </si>
+  <si>
+    <t>peak sampling circuits not working correctly</t>
+  </si>
+  <si>
+    <t>check assembly, resolder connections?</t>
+  </si>
+  <si>
+    <t>low pass and attenuator circuits not designed right. No signal comes out to ~1.5V, and a signal being present doesn't change much</t>
+  </si>
+  <si>
+    <t>maybe ground of capacitor should go to 14V offset instead of ground?</t>
   </si>
 </sst>
 </file>
@@ -125,11 +158,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -411,22 +447,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:F11"/>
+  <dimension ref="B1:F14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="71.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" customWidth="1"/>
+    <col min="4" max="4" width="59.140625" customWidth="1"/>
     <col min="5" max="5" width="86" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" s="1">
         <v>45822</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="2" t="s">
@@ -443,7 +496,7 @@
       <c r="C4" s="1">
         <v>45822</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E4" t="s">
@@ -460,7 +513,7 @@
       <c r="C5" s="1">
         <v>45823</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E5" t="s">
@@ -477,7 +530,7 @@
       <c r="C6" s="1">
         <v>45845</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E6" t="s">
@@ -494,7 +547,7 @@
       <c r="C7" s="1">
         <v>45845</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E7" t="s">
@@ -511,7 +564,7 @@
       <c r="C8" s="1">
         <v>45846</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E8" t="s">
@@ -520,6 +573,9 @@
       <c r="F8" t="s">
         <v>16</v>
       </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D9" s="3"/>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10">
@@ -528,7 +584,7 @@
       <c r="C10" s="1">
         <v>45860</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E10" t="s">
@@ -538,20 +594,71 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>9</v>
       </c>
       <c r="C11" s="1">
         <v>45862</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E11" t="s">
         <v>14</v>
       </c>
       <c r="F11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="B12">
+        <v>10</v>
+      </c>
+      <c r="C12" s="1">
+        <v>45888</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B13">
+        <v>11</v>
+      </c>
+      <c r="C13" s="1">
+        <v>45888</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="B14">
+        <v>12</v>
+      </c>
+      <c r="C14" s="1">
+        <v>45888</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" t="s">
         <v>15</v>
       </c>
     </row>

--- a/Hardware/Design/Issue Log.xlsx
+++ b/Hardware/Design/Issue Log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://indesignllc1-my.sharepoint.com/personal/adwolfe_indesign-llc_com/Documents/M_Drive/Github/Home-Audio-System/Hardware/Design/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/69f5ad8fb782b24f/Documents/GitHub/Home-Audio-System/Hardware/Design/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="96" documentId="11_F25DC773A252ABDACC1048A061DA4FC05ADE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68EBBC3B-8D0D-43E5-BF62-F9840F2286C4}"/>
+  <xr:revisionPtr revIDLastSave="131" documentId="11_F25DC773A252ABDACC1048A061DA4FC05ADE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6594086E-2926-4253-ABE0-680F2714F7DD}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="33">
   <si>
     <t>All input sources cannot be selected</t>
   </si>
@@ -122,7 +122,19 @@
     <t>low pass and attenuator circuits not designed right. No signal comes out to ~1.5V, and a signal being present doesn't change much</t>
   </si>
   <si>
-    <t>maybe ground of capacitor should go to 14V offset instead of ground?</t>
+    <t>Replace all resistors on low pass filtering and attenuation page with 100k. Add 2 100k negative feedback resistors on every op amp output, that are referenced at 14V offset. This builds subtractor circuit to do this properly</t>
+  </si>
+  <si>
+    <t>implemented in design files?</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>aux channel volume is very low from phone output</t>
+  </si>
+  <si>
+    <t>increase resistance of R173 and R174</t>
   </si>
 </sst>
 </file>
@@ -146,7 +158,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -154,18 +166,41 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -447,7 +482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:F14"/>
+  <dimension ref="B1:G15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.85546875" customWidth="1"/>
@@ -455,7 +490,7 @@
     <col min="5" max="5" width="86" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>18</v>
       </c>
@@ -471,196 +506,250 @@
       <c r="F1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B3">
+      <c r="G1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="4">
         <v>1</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="5">
         <v>45822</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4">
+      <c r="G3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="4">
         <v>2</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="5">
         <v>45822</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B5">
+      <c r="G4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="4">
         <v>3</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="5">
         <v>45823</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B6">
+      <c r="G5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="4">
         <v>4</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="5">
         <v>45845</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7">
+      <c r="G6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="4">
         <v>5</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="5">
         <v>45845</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="4">
+        <v>6</v>
+      </c>
+      <c r="C8" s="5">
+        <v>45846</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="4">
+        <v>7</v>
+      </c>
+      <c r="C9" s="5">
+        <v>45889</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" s="3"/>
+      <c r="G9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="4">
+        <v>8</v>
+      </c>
+      <c r="C10" s="5">
+        <v>45860</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B11" s="4">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>45862</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B12" s="4">
+        <v>10</v>
+      </c>
+      <c r="C12" s="5">
+        <v>45888</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8">
-        <v>6</v>
-      </c>
-      <c r="C8" s="1">
-        <v>45846</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="G12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="4">
         <v>11</v>
       </c>
-      <c r="F8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="D9" s="3"/>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B10">
-        <v>8</v>
-      </c>
-      <c r="C10" s="1">
-        <v>45860</v>
-      </c>
-      <c r="D10" s="3" t="s">
+      <c r="C13" s="5">
+        <v>45888</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="B14" s="4">
         <v>12</v>
       </c>
-      <c r="E10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="B11">
-        <v>9</v>
-      </c>
-      <c r="C11" s="1">
-        <v>45862</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="B12">
-        <v>10</v>
-      </c>
-      <c r="C12" s="1">
+      <c r="C14" s="5">
         <v>45888</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="D14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B13">
-        <v>11</v>
-      </c>
-      <c r="C13" s="1">
-        <v>45888</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" t="s">
-        <v>26</v>
-      </c>
-      <c r="F13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="B14">
-        <v>12</v>
-      </c>
-      <c r="C14" s="1">
-        <v>45888</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" t="s">
-        <v>28</v>
-      </c>
-      <c r="F14" t="s">
-        <v>15</v>
-      </c>
+      <c r="G14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="F15" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Hardware/Design/Issue Log.xlsx
+++ b/Hardware/Design/Issue Log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/69f5ad8fb782b24f/Documents/GitHub/Home-Audio-System/Hardware/Design/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://indesignllc1-my.sharepoint.com/personal/adwolfe_indesign-llc_com/Documents/M_Drive/Github/Home-Audio-System/Hardware/Design/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="131" documentId="11_F25DC773A252ABDACC1048A061DA4FC05ADE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6594086E-2926-4253-ABE0-680F2714F7DD}"/>
+  <xr:revisionPtr revIDLastSave="134" documentId="11_F25DC773A252ABDACC1048A061DA4FC05ADE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{360921C4-79AD-4E43-9CFC-3A72331FE666}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="35">
   <si>
     <t>All input sources cannot be selected</t>
   </si>
@@ -135,6 +135,12 @@
   </si>
   <si>
     <t>increase resistance of R173 and R174</t>
+  </si>
+  <si>
+    <t>output audio oscillates at around 23MHz when speaker is connected, open load is fine</t>
+  </si>
+  <si>
+    <t>add compensation network</t>
   </si>
 </sst>
 </file>
@@ -185,11 +191,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -511,19 +514,19 @@
       </c>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="4">
+      <c r="B3" s="3">
         <v>1</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="4">
         <v>45822</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G3" t="s">
@@ -531,19 +534,19 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="4">
+      <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="4">
         <v>45822</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G4" t="s">
@@ -551,19 +554,19 @@
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="4">
+      <c r="B5" s="3">
         <v>3</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="4">
         <v>45823</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G5" t="s">
@@ -571,19 +574,19 @@
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="4">
+      <c r="B6" s="3">
         <v>4</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="4">
         <v>45845</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G6" t="s">
@@ -591,19 +594,19 @@
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="4">
+      <c r="B7" s="3">
         <v>5</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="4">
         <v>45845</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G7" t="s">
@@ -611,19 +614,19 @@
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="4">
+      <c r="B8" s="3">
         <v>6</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="4">
         <v>45846</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G8" t="s">
@@ -631,37 +634,37 @@
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="4">
+      <c r="B9" s="3">
         <v>7</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="4">
         <v>45889</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="3"/>
+      <c r="F9" s="2"/>
       <c r="G9" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="4">
+      <c r="B10" s="3">
         <v>8</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="4">
         <v>45860</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G10" t="s">
@@ -669,19 +672,19 @@
       </c>
     </row>
     <row r="11" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B11" s="4">
+      <c r="B11" s="3">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="4">
         <v>45862</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G11" t="s">
@@ -689,19 +692,19 @@
       </c>
     </row>
     <row r="12" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B12" s="4">
+      <c r="B12" s="3">
         <v>10</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="4">
         <v>45888</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G12" t="s">
@@ -709,19 +712,19 @@
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="4">
+      <c r="B13" s="3">
         <v>11</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="4">
         <v>45888</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G13" t="s">
@@ -729,27 +732,44 @@
       </c>
     </row>
     <row r="14" spans="2:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="B14" s="4">
+      <c r="B14" s="3">
         <v>12</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="4">
         <v>45888</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G14" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="F15" s="1"/>
+    <row r="15" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B15" s="3">
+        <v>13</v>
+      </c>
+      <c r="C15" s="4">
+        <v>45890</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" t="s">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Hardware/Design/Issue Log.xlsx
+++ b/Hardware/Design/Issue Log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://indesignllc1-my.sharepoint.com/personal/adwolfe_indesign-llc_com/Documents/M_Drive/Github/Home-Audio-System/Hardware/Design/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/69f5ad8fb782b24f/Documents/GitHub/Home-Audio-System/Hardware/Design/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="134" documentId="11_F25DC773A252ABDACC1048A061DA4FC05ADE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{360921C4-79AD-4E43-9CFC-3A72331FE666}"/>
+  <xr:revisionPtr revIDLastSave="135" documentId="11_F25DC773A252ABDACC1048A061DA4FC05ADE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FC401C2-499D-4E7B-AEA2-6494D72CF202}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19560" yWindow="810" windowWidth="15420" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -140,7 +140,7 @@
     <t>output audio oscillates at around 23MHz when speaker is connected, open load is fine</t>
   </si>
   <si>
-    <t>add compensation network</t>
+    <t>add compensation network, check how 14Voffset voltage is doing</t>
   </si>
 </sst>
 </file>

--- a/Hardware/Design/Issue Log.xlsx
+++ b/Hardware/Design/Issue Log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/69f5ad8fb782b24f/Documents/GitHub/Home-Audio-System/Hardware/Design/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://indesignllc1-my.sharepoint.com/personal/adwolfe_indesign-llc_com/Documents/M_Drive/Github/Home-Audio-System/Hardware/Design/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="135" documentId="11_F25DC773A252ABDACC1048A061DA4FC05ADE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FC401C2-499D-4E7B-AEA2-6494D72CF202}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{B2280FC0-F47C-4725-B472-25304032D7F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B48C63A-C0FA-4EE4-935E-C836D9903AFD}"/>
   <bookViews>
-    <workbookView xWindow="19560" yWindow="810" windowWidth="15420" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31500" yWindow="810" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -140,7 +140,7 @@
     <t>output audio oscillates at around 23MHz when speaker is connected, open load is fine</t>
   </si>
   <si>
-    <t>add compensation network, check how 14Voffset voltage is doing</t>
+    <t>add compensation network 200 ohm and 6.8nF where DNA pads are, 8pF feed forward across 2k, check how 14Voffset voltage is doing</t>
   </si>
 </sst>
 </file>

--- a/Hardware/Design/Issue Log.xlsx
+++ b/Hardware/Design/Issue Log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://indesignllc1-my.sharepoint.com/personal/adwolfe_indesign-llc_com/Documents/M_Drive/Github/Home-Audio-System/Hardware/Design/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/69f5ad8fb782b24f/Documents/GitHub/Home-Audio-System/Hardware/Design/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{B2280FC0-F47C-4725-B472-25304032D7F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B48C63A-C0FA-4EE4-935E-C836D9903AFD}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{B2280FC0-F47C-4725-B472-25304032D7F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A0A907D-58A1-4477-899A-4F6E78E6E4C2}"/>
   <bookViews>
-    <workbookView xWindow="31500" yWindow="810" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12735" yWindow="1905" windowWidth="15420" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="39">
   <si>
     <t>All input sources cannot be selected</t>
   </si>
@@ -140,7 +140,19 @@
     <t>output audio oscillates at around 23MHz when speaker is connected, open load is fine</t>
   </si>
   <si>
-    <t>add compensation network 200 ohm and 6.8nF where DNA pads are, 8pF feed forward across 2k, check how 14Voffset voltage is doing</t>
+    <t>compensator circuit, see ltspice sim. 10pF capacitor from output to inverting terminal to take power amp out of feedback loop at high frequency. Consider 500ohm + 3000pF compensator circuit</t>
+  </si>
+  <si>
+    <t>Connecting phone to aux input causes DC voltage to appear at output. Takes a long time to dissipate</t>
+  </si>
+  <si>
+    <t>Change pullup resistors to 2V5 to 10k instead of 1Meg</t>
+  </si>
+  <si>
+    <t>volume of zero is still audible</t>
+  </si>
+  <si>
+    <t>use shutdown feature of digipot (firmware change)</t>
   </si>
 </sst>
 </file>
@@ -191,19 +203,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -485,11 +507,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:G15"/>
+  <dimension ref="B1:G17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.85546875" customWidth="1"/>
-    <col min="4" max="4" width="59.140625" customWidth="1"/>
+    <col min="4" max="4" width="58.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="86" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -514,10 +536,10 @@
       </c>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <v>1</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="3">
         <v>45822</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -526,18 +548,18 @@
       <c r="E3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="F3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <v>2</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="3">
         <v>45822</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -546,18 +568,18 @@
       <c r="E4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="F4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>3</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="3">
         <v>45823</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -566,18 +588,18 @@
       <c r="E5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="F5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="7" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>4</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="3">
         <v>45845</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -586,18 +608,18 @@
       <c r="E6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="7" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <v>5</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="3">
         <v>45845</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -606,18 +628,18 @@
       <c r="E7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="7" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <v>6</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="3">
         <v>45846</v>
       </c>
       <c r="D8" s="1" t="s">
@@ -626,18 +648,18 @@
       <c r="E8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="7" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="3">
+      <c r="B9" s="2">
         <v>7</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="3">
         <v>45889</v>
       </c>
       <c r="D9" s="1" t="s">
@@ -646,16 +668,18 @@
       <c r="E9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="2"/>
-      <c r="G9" t="s">
+      <c r="F9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="3">
+      <c r="B10" s="2">
         <v>8</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="3">
         <v>45860</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -664,18 +688,18 @@
       <c r="E10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="7" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B11" s="3">
+      <c r="B11" s="2">
         <v>9</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="3">
         <v>45862</v>
       </c>
       <c r="D11" s="1" t="s">
@@ -684,18 +708,18 @@
       <c r="E11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="7" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B12" s="3">
+      <c r="B12" s="2">
         <v>10</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="3">
         <v>45888</v>
       </c>
       <c r="D12" s="1" t="s">
@@ -704,18 +728,18 @@
       <c r="E12" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12" t="s">
+      <c r="F12" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="7" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="3">
+      <c r="B13" s="2">
         <v>11</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="3">
         <v>45888</v>
       </c>
       <c r="D13" s="1" t="s">
@@ -724,18 +748,18 @@
       <c r="E13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" t="s">
+      <c r="F13" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="7" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="14" spans="2:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="B14" s="3">
+      <c r="B14" s="2">
         <v>12</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="3">
         <v>45888</v>
       </c>
       <c r="D14" s="1" t="s">
@@ -744,18 +768,18 @@
       <c r="E14" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B15" s="3">
+      <c r="F14" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="B15" s="2">
         <v>13</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="3">
         <v>45890</v>
       </c>
       <c r="D15" s="1" t="s">
@@ -764,10 +788,50 @@
       <c r="E15" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" t="s">
+      <c r="F15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B16" s="4">
+        <v>14</v>
+      </c>
+      <c r="C16" s="5">
+        <v>45903</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="4">
+        <v>15</v>
+      </c>
+      <c r="C17" s="5">
+        <v>45903</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="7" t="s">
         <v>30</v>
       </c>
     </row>

--- a/Hardware/Design/Issue Log.xlsx
+++ b/Hardware/Design/Issue Log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/69f5ad8fb782b24f/Documents/GitHub/Home-Audio-System/Hardware/Design/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://indesignllc1-my.sharepoint.com/personal/adwolfe_indesign-llc_com/Documents/M_Drive/Github/Home-Audio-System/Hardware/Design/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{B2280FC0-F47C-4725-B472-25304032D7F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A0A907D-58A1-4477-899A-4F6E78E6E4C2}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{B2280FC0-F47C-4725-B472-25304032D7F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A9A428F-80DA-4C40-BAAA-4471F9407627}"/>
   <bookViews>
-    <workbookView xWindow="12735" yWindow="1905" windowWidth="15420" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="41">
   <si>
     <t>All input sources cannot be selected</t>
   </si>
@@ -153,6 +153,12 @@
   </si>
   <si>
     <t>use shutdown feature of digipot (firmware change)</t>
+  </si>
+  <si>
+    <t>use good quality caps around zener-like circuit in output stage</t>
+  </si>
+  <si>
+    <t>reduce distortion</t>
   </si>
 </sst>
 </file>
@@ -176,7 +182,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -199,11 +205,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -214,17 +231,14 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -507,7 +521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:G17"/>
+  <dimension ref="B1:G18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.85546875" customWidth="1"/>
@@ -548,10 +562,10 @@
       <c r="E3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="7" t="s">
+      <c r="F3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>30</v>
       </c>
     </row>
@@ -568,10 +582,10 @@
       <c r="E4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="7" t="s">
+      <c r="F4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>30</v>
       </c>
     </row>
@@ -588,10 +602,10 @@
       <c r="E5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="7" t="s">
+      <c r="F5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>30</v>
       </c>
     </row>
@@ -608,10 +622,10 @@
       <c r="E6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="5" t="s">
         <v>30</v>
       </c>
     </row>
@@ -628,10 +642,10 @@
       <c r="E7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="5" t="s">
         <v>30</v>
       </c>
     </row>
@@ -648,10 +662,10 @@
       <c r="E8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="5" t="s">
         <v>30</v>
       </c>
     </row>
@@ -668,10 +682,10 @@
       <c r="E9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" s="7" t="s">
+      <c r="F9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>30</v>
       </c>
     </row>
@@ -688,10 +702,10 @@
       <c r="E10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="5" t="s">
         <v>30</v>
       </c>
     </row>
@@ -708,10 +722,10 @@
       <c r="E11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="5" t="s">
         <v>30</v>
       </c>
     </row>
@@ -728,10 +742,10 @@
       <c r="E12" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F12" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12" s="7" t="s">
+      <c r="F12" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>30</v>
       </c>
     </row>
@@ -748,10 +762,10 @@
       <c r="E13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F13" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" s="7" t="s">
+      <c r="F13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="5" t="s">
         <v>30</v>
       </c>
     </row>
@@ -768,10 +782,10 @@
       <c r="E14" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F14" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" s="7" t="s">
+      <c r="F14" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>30</v>
       </c>
     </row>
@@ -788,50 +802,64 @@
       <c r="E15" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F15" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" s="7" t="s">
+      <c r="F15" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B16" s="4">
+      <c r="B16" s="2">
         <v>14</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="4">
         <v>45903</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F16" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16" s="7" t="s">
+      <c r="F16" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="5" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="4">
-        <v>15</v>
-      </c>
-      <c r="C17" s="5">
+      <c r="B17" s="2">
+        <v>15</v>
+      </c>
+      <c r="C17" s="4">
         <v>45903</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F17" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" s="7" t="s">
+      <c r="F17" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="D18" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" s="7" t="s">
         <v>30</v>
       </c>
     </row>
